--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N121_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N121_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.71333228013283</v>
+        <v>7.265916495521585</v>
       </c>
       <c r="D2" t="n">
-        <v>30.10398644698074</v>
+        <v>4.89189779763437</v>
       </c>
       <c r="E2" t="n">
-        <v>8.182028597660631</v>
+        <v>1.329579647119853</v>
       </c>
       <c r="F2" t="n">
-        <v>13.7720498998674</v>
+        <v>2.237958108728452</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.83490754203606</v>
+        <v>8.26067247558086</v>
       </c>
       <c r="D3" t="n">
-        <v>51.04952624989613</v>
+        <v>8.295548015608121</v>
       </c>
       <c r="E3" t="n">
-        <v>8.182028597660631</v>
+        <v>1.329579647119853</v>
       </c>
       <c r="F3" t="n">
-        <v>13.7720498998674</v>
+        <v>2.237958108728452</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.43634562446865</v>
+        <v>4.620906163976155</v>
       </c>
       <c r="D4" t="n">
-        <v>45.1807246128613</v>
+        <v>7.341867749589961</v>
       </c>
       <c r="E4" t="n">
-        <v>8.182028597660631</v>
+        <v>1.329579647119853</v>
       </c>
       <c r="F4" t="n">
-        <v>13.7720498998674</v>
+        <v>2.237958108728452</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.75078002690427</v>
+        <v>7.597001754371945</v>
       </c>
       <c r="D5" t="n">
-        <v>35.36895101971968</v>
+        <v>5.747454540704449</v>
       </c>
       <c r="E5" t="n">
-        <v>8.182028597660631</v>
+        <v>1.329579647119853</v>
       </c>
       <c r="F5" t="n">
-        <v>13.7720498998674</v>
+        <v>2.237958108728452</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.23438327624692</v>
+        <v>7.025587282390125</v>
       </c>
       <c r="D6" t="n">
-        <v>9.500310842907883</v>
+        <v>1.543800511972531</v>
       </c>
       <c r="E6" t="n">
-        <v>8.182028597660631</v>
+        <v>1.329579647119853</v>
       </c>
       <c r="F6" t="n">
-        <v>13.7720498998674</v>
+        <v>2.237958108728452</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.07764817404063</v>
+        <v>6.675117828281603</v>
       </c>
       <c r="D7" t="n">
-        <v>6.461642182303196</v>
+        <v>1.050016854624269</v>
       </c>
       <c r="E7" t="n">
-        <v>8.182028597660631</v>
+        <v>1.329579647119853</v>
       </c>
       <c r="F7" t="n">
-        <v>13.7720498998674</v>
+        <v>2.237958108728452</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>48.29495354471206</v>
+        <v>7.847929951015709</v>
       </c>
       <c r="D8" t="n">
-        <v>15.68919908217969</v>
+        <v>2.549494850854199</v>
       </c>
       <c r="E8" t="n">
-        <v>8.182028597660631</v>
+        <v>1.329579647119853</v>
       </c>
       <c r="F8" t="n">
-        <v>13.7720498998674</v>
+        <v>2.237958108728452</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>52.28239278216667</v>
+        <v>8.495888827102084</v>
       </c>
       <c r="D9" t="n">
-        <v>20.49502450763753</v>
+        <v>3.330441482491098</v>
       </c>
       <c r="E9" t="n">
-        <v>8.182028597660631</v>
+        <v>1.329579647119853</v>
       </c>
       <c r="F9" t="n">
-        <v>13.7720498998674</v>
+        <v>2.237958108728452</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>52.17598795268066</v>
+        <v>8.478598042310606</v>
       </c>
       <c r="D10" t="n">
-        <v>26.81877414895419</v>
+        <v>4.358050799205055</v>
       </c>
       <c r="E10" t="n">
-        <v>8.182028597660631</v>
+        <v>1.329579647119853</v>
       </c>
       <c r="F10" t="n">
-        <v>13.7720498998674</v>
+        <v>2.237958108728452</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>29.50358969715126</v>
+        <v>4.79433332578708</v>
       </c>
       <c r="D11" t="n">
-        <v>30.13373949692859</v>
+        <v>4.896732668250896</v>
       </c>
       <c r="E11" t="n">
-        <v>8.182028597660631</v>
+        <v>1.329579647119853</v>
       </c>
       <c r="F11" t="n">
-        <v>13.7720498998674</v>
+        <v>2.237958108728452</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
